--- a/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C093C79-C19E-4019-B250-71C07CC46429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C400A83B-EB24-4FA0-B14B-1D74D44E31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1029,10 +1029,10 @@
     <t>Trd_electricity import</t>
   </si>
   <si>
-    <t>e_w111615226-380,e_w139452056-400,e_w166838338-400,e_w173613665-220,e_w183945016-220,e_w215282393-400,e_w255277953-400,e_w303870256-400,e_w39428977-400,e_w44389929-220</t>
-  </si>
-  <si>
     <t>Trd_electricity export</t>
+  </si>
+  <si>
+    <t>e_gen1,e_gen2,e_gen3</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1672,7 @@
         <v>300</v>
       </c>
       <c r="AI4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ4" t="s">
         <v>197</v>
@@ -1743,10 +1743,10 @@
         <v>298</v>
       </c>
       <c r="AH5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AI5" t="s">
         <v>302</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>301</v>
       </c>
       <c r="AJ5" t="s">
         <v>189</v>

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C400A83B-EB24-4FA0-B14B-1D74D44E31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D06B95-7F48-4F27-B8B6-F18D37F2597C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="304">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1033,6 +1033,9 @@
   </si>
   <si>
     <t>e_gen1,e_gen2,e_gen3</t>
+  </si>
+  <si>
+    <t>stgin_bnd</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1591,7 @@
       <c r="X3" t="s">
         <v>187</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="Z3" t="s">
         <v>160</v>
       </c>
       <c r="AH3" t="s">
@@ -1650,17 +1653,20 @@
       <c r="X4" t="s">
         <v>197</v>
       </c>
+      <c r="Z4" t="s">
+        <v>161</v>
+      </c>
       <c r="AA4" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="AB4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AC4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AD4" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AE4" t="s">
         <v>296</v>
@@ -1727,13 +1733,13 @@
       <c r="X5" t="s">
         <v>197</v>
       </c>
+      <c r="Z5" t="s">
+        <v>291</v>
+      </c>
       <c r="AA5" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB5" t="s">
         <v>293</v>
       </c>
-      <c r="AC5">
+      <c r="AB5">
         <v>2</v>
       </c>
       <c r="AE5">
@@ -1801,13 +1807,13 @@
       <c r="X6" t="s">
         <v>197</v>
       </c>
+      <c r="Z6" t="s">
+        <v>291</v>
+      </c>
       <c r="AA6" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB6" t="s">
         <v>293</v>
       </c>
-      <c r="AD6">
+      <c r="AC6">
         <v>2</v>
       </c>
       <c r="AE6">
@@ -1865,6 +1871,21 @@
       </c>
       <c r="X7" t="s">
         <v>197</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD7">
+        <v>2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.45">

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C0AD0E4-417D-4416-9371-ED37945519BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36934602-4CF9-4B6A-992E-16538CAB9B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1638,7 +1638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B0D796-B55D-4ACB-B7FF-C6FE933B766E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D37A93-22E2-487A-AD78-15C953F13E0B}">
   <dimension ref="B2:AF93"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4283,7 +4283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3778A5-8D26-4AD5-A1B0-D3C851D0DF2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E56863-42AA-48A3-80B6-26F1DE6220F9}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36934602-4CF9-4B6A-992E-16538CAB9B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46326273-D727-44D3-B987-E21BADD17F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="313">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -548,7 +548,13 @@
     <t>g_dem2-dem0</t>
   </si>
   <si>
-    <t>g_gen0-dem0</t>
+    <t>g_gen0-dem3</t>
+  </si>
+  <si>
+    <t>g_gen0-dem4</t>
+  </si>
+  <si>
+    <t>g_gen1-dem0</t>
   </si>
   <si>
     <t>g_gen1-dem1</t>
@@ -557,10 +563,13 @@
     <t>g_gen1-dem2</t>
   </si>
   <si>
-    <t>g_gen2-dem3</t>
-  </si>
-  <si>
-    <t>g_gen2-dem4</t>
+    <t>g_gen1-dem4</t>
+  </si>
+  <si>
+    <t>g_gen2-dem1</t>
+  </si>
+  <si>
+    <t>g_gen2-dem2</t>
   </si>
   <si>
     <t>g_gen3-dem0</t>
@@ -572,15 +581,6 @@
     <t>g_gen4-dem0</t>
   </si>
   <si>
-    <t>g_gen4-dem1</t>
-  </si>
-  <si>
-    <t>g_gen4-dem2</t>
-  </si>
-  <si>
-    <t>g_gen4-dem4</t>
-  </si>
-  <si>
     <t>g_sol1-dem2</t>
   </si>
   <si>
@@ -599,22 +599,22 @@
     <t>g_sol14-dem1</t>
   </si>
   <si>
-    <t>g_sol15-gen1</t>
-  </si>
-  <si>
-    <t>g_sol16-gen4</t>
-  </si>
-  <si>
-    <t>g_sol17-gen4</t>
+    <t>g_sol15-gen2</t>
+  </si>
+  <si>
+    <t>g_sol16-gen1</t>
+  </si>
+  <si>
+    <t>g_sol17-gen1</t>
   </si>
   <si>
     <t>g_sol18-dem4</t>
   </si>
   <si>
-    <t>g_sol19-gen2</t>
-  </si>
-  <si>
-    <t>g_sol2-gen1</t>
+    <t>g_sol19-gen0</t>
+  </si>
+  <si>
+    <t>g_sol2-gen2</t>
   </si>
   <si>
     <t>g_sol3-dem2</t>
@@ -629,7 +629,7 @@
     <t>g_sol6-dem0</t>
   </si>
   <si>
-    <t>g_sol7-gen0</t>
+    <t>g_sol7-gen4</t>
   </si>
   <si>
     <t>g_sol8-dem0</t>
@@ -638,49 +638,7 @@
     <t>g_sol9-dem4</t>
   </si>
   <si>
-    <t>g_wof0-gen1</t>
-  </si>
-  <si>
-    <t>g_wof1-dem0</t>
-  </si>
-  <si>
-    <t>g_wof10-gen0</t>
-  </si>
-  <si>
-    <t>g_wof2-gen0</t>
-  </si>
-  <si>
-    <t>g_wof3-dem0</t>
-  </si>
-  <si>
-    <t>g_wof4-gen0</t>
-  </si>
-  <si>
-    <t>g_wof5-gen0</t>
-  </si>
-  <si>
-    <t>g_wof6-gen0</t>
-  </si>
-  <si>
-    <t>g_wof7-gen3</t>
-  </si>
-  <si>
-    <t>g_wof8-gen0</t>
-  </si>
-  <si>
-    <t>g_wof9-gen0</t>
-  </si>
-  <si>
-    <t>g_won0-gen2</t>
-  </si>
-  <si>
-    <t>g_won1-gen2</t>
-  </si>
-  <si>
-    <t>g_won10-gen0</t>
-  </si>
-  <si>
-    <t>g_won11-dem2</t>
+    <t>g_won0-gen0</t>
   </si>
   <si>
     <t>g_won12-dem2</t>
@@ -689,45 +647,9 @@
     <t>g_won13-dem2</t>
   </si>
   <si>
-    <t>g_won14-dem2</t>
-  </si>
-  <si>
-    <t>g_won15-dem1</t>
-  </si>
-  <si>
-    <t>g_won16-dem3</t>
-  </si>
-  <si>
-    <t>g_won17-dem3</t>
-  </si>
-  <si>
     <t>g_won18-dem2</t>
   </si>
   <si>
-    <t>g_won19-dem1</t>
-  </si>
-  <si>
-    <t>g_won2-dem3</t>
-  </si>
-  <si>
-    <t>g_won3-dem4</t>
-  </si>
-  <si>
-    <t>g_won4-dem3</t>
-  </si>
-  <si>
-    <t>g_won5-dem4</t>
-  </si>
-  <si>
-    <t>g_won6-gen4</t>
-  </si>
-  <si>
-    <t>g_won7-dem4</t>
-  </si>
-  <si>
-    <t>g_won8-dem0</t>
-  </si>
-  <si>
     <t>g_won9-dem0</t>
   </si>
   <si>
@@ -836,15 +758,57 @@
     <t>region</t>
   </si>
   <si>
+    <t>Bioenergy + CCUS_gen2</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_gen2</t>
+  </si>
+  <si>
+    <t>CCGT_gen2</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_gen2</t>
+  </si>
+  <si>
+    <t>Coal + CCS_gen2</t>
+  </si>
+  <si>
+    <t>Gas turbine_gen2</t>
+  </si>
+  <si>
+    <t>IGCC_gen2</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_gen2</t>
+  </si>
+  <si>
+    <t>Nuclear large_gen2</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_gen2</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_gen2</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_gen2</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_gen2</t>
+  </si>
+  <si>
     <t>Bioenergy + CCUS_gen1</t>
   </si>
   <si>
     <t>e_gen1</t>
   </si>
   <si>
-    <t>OUT</t>
-  </si>
-  <si>
     <t>Bioenergy - Large scale unit_gen1</t>
   </si>
   <si>
@@ -965,48 +929,6 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_gen0</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS_gen2</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>Bioenergy - Large scale unit_gen2</t>
-  </si>
-  <si>
-    <t>CCGT_gen2</t>
-  </si>
-  <si>
-    <t>CCGT + CCS_gen2</t>
-  </si>
-  <si>
-    <t>Coal + CCS_gen2</t>
-  </si>
-  <si>
-    <t>Gas turbine_gen2</t>
-  </si>
-  <si>
-    <t>IGCC_gen2</t>
-  </si>
-  <si>
-    <t>IGCC + CCS_gen2</t>
-  </si>
-  <si>
-    <t>Nuclear large_gen2</t>
-  </si>
-  <si>
-    <t>Oxyfuel + CCS_gen2</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUBCRITICAL_gen2</t>
-  </si>
-  <si>
-    <t>Steam Coal - SUPERCRITICAL_gen2</t>
-  </si>
-  <si>
-    <t>Steam Coal - ULTRASUPERCRITICAL_gen2</t>
-  </si>
-  <si>
     <t>Bioenergy + CCUS_gen3</t>
   </si>
   <si>
@@ -1058,6 +980,24 @@
     <t>EN_Hydro_POL-3_gen3</t>
   </si>
   <si>
+    <t>EN_Hydro_POL-1_gen2</t>
+  </si>
+  <si>
+    <t>EN_Hydro_POL-2_gen2</t>
+  </si>
+  <si>
+    <t>EN_Hydro_POL-3_gen2</t>
+  </si>
+  <si>
+    <t>EN_Hydro_POL-1_gen0</t>
+  </si>
+  <si>
+    <t>EN_Hydro_POL-2_gen0</t>
+  </si>
+  <si>
+    <t>EN_Hydro_POL-3_gen0</t>
+  </si>
+  <si>
     <t>EN_Hydro_POL-1_gen1</t>
   </si>
   <si>
@@ -1076,22 +1016,10 @@
     <t>EN_Hydro_POL-3_gen4</t>
   </si>
   <si>
-    <t>EN_Hydro_POL-1_gen2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_POL-2_gen2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_POL-3_gen2</t>
-  </si>
-  <si>
-    <t>EN_Hydro_POL-1_gen0</t>
-  </si>
-  <si>
-    <t>EN_Hydro_POL-2_gen0</t>
-  </si>
-  <si>
-    <t>EN_Hydro_POL-3_gen0</t>
+    <t>EN_STG8hbNREL_gen2</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_gen2</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_gen1</t>
@@ -1110,12 +1038,6 @@
   </si>
   <si>
     <t>EN_STG4hbNREL_gen0</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_gen2</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_gen2</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_gen3</t>
@@ -1638,7 +1560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D37A93-22E2-487A-AD78-15C953F13E0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49A8FD2-364F-42DB-8D42-E715B8153167}">
   <dimension ref="B2:AF93"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1647,13 +1569,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
+        <v>173</v>
+      </c>
+      <c r="P2" t="s">
         <v>199</v>
       </c>
-      <c r="P2" t="s">
-        <v>225</v>
-      </c>
       <c r="U2" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="2:32" x14ac:dyDescent="0.45">
@@ -1673,13 +1595,13 @@
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="J3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="K3" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="L3" t="s">
         <v>14</v>
@@ -1688,25 +1610,25 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R3" t="s">
         <v>200</v>
       </c>
-      <c r="R3" t="s">
-        <v>226</v>
-      </c>
       <c r="U3" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
       </c>
       <c r="W3" t="s">
+        <v>174</v>
+      </c>
+      <c r="X3" t="s">
         <v>200</v>
       </c>
-      <c r="X3" t="s">
-        <v>226</v>
-      </c>
       <c r="AA3" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.45">
@@ -1723,58 +1645,58 @@
         <v>0.97852000000000006</v>
       </c>
       <c r="H4" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="I4" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J4">
         <v>0.15192763072402418</v>
       </c>
       <c r="K4" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L4" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P4" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="Q4" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="R4" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U4" t="s">
         <v>130</v>
       </c>
       <c r="V4" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="W4" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X4" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="AA4" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="AB4" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="AC4" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="AD4" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="AE4" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="AF4" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.45">
@@ -1791,46 +1713,46 @@
         <v>0.98829999999999996</v>
       </c>
       <c r="H5" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="I5" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J5">
         <v>0.29667399283427875</v>
       </c>
       <c r="K5" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L5" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="Q5" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="R5" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U5" t="s">
         <v>130</v>
       </c>
       <c r="V5" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="W5" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X5" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="AA5" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="AB5" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -1839,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.45">
@@ -1856,46 +1778,46 @@
         <v>0.98373999999999995</v>
       </c>
       <c r="H6" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="I6" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J6">
         <v>0.21267178371296797</v>
       </c>
       <c r="K6" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P6" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q6" t="s">
         <v>204</v>
       </c>
-      <c r="P6" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>230</v>
-      </c>
       <c r="R6" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U6" t="s">
         <v>130</v>
       </c>
       <c r="V6" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="W6" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X6" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="AA6" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="AB6" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -1904,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.45">
@@ -1921,40 +1843,40 @@
         <v>0.98560000000000003</v>
       </c>
       <c r="H7" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="I7" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J7">
         <v>0.11770917700286149</v>
       </c>
       <c r="K7" t="s">
+        <v>179</v>
+      </c>
+      <c r="L7" t="s">
+        <v>178</v>
+      </c>
+      <c r="P7" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q7" t="s">
         <v>205</v>
       </c>
-      <c r="L7" t="s">
-        <v>204</v>
-      </c>
-      <c r="P7" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>231</v>
-      </c>
       <c r="R7" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U7" t="s">
         <v>130</v>
       </c>
       <c r="V7" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="W7" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X7" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.45">
@@ -1962,49 +1884,49 @@
         <v>138</v>
       </c>
       <c r="C8">
-        <v>15.774477999999998</v>
+        <v>22.522200000000002</v>
       </c>
       <c r="D8">
-        <v>183.70000000000002</v>
+        <v>108.9</v>
       </c>
       <c r="E8">
-        <v>0.98997999999999997</v>
+        <v>0.99406000000000005</v>
       </c>
       <c r="H8" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="I8" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J8">
         <v>0.20101741572586737</v>
       </c>
       <c r="K8" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L8" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="Q8" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="R8" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U8" t="s">
         <v>130</v>
       </c>
       <c r="V8" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="W8" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X8" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.45">
@@ -2012,49 +1934,49 @@
         <v>139</v>
       </c>
       <c r="C9">
-        <v>33.693925999999998</v>
+        <v>62.293548999999999</v>
       </c>
       <c r="D9">
-        <v>24.200000000000003</v>
+        <v>119.9</v>
       </c>
       <c r="E9">
-        <v>0.99868000000000001</v>
+        <v>0.99346000000000001</v>
       </c>
       <c r="H9" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="I9" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J9">
         <v>0.15192763072402418</v>
       </c>
       <c r="K9" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L9" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="Q9" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="R9" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U9" t="s">
         <v>130</v>
       </c>
       <c r="V9" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="W9" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X9" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.45">
@@ -2062,49 +1984,49 @@
         <v>140</v>
       </c>
       <c r="C10">
-        <v>7.6414610000000005</v>
+        <v>37.760435999999999</v>
       </c>
       <c r="D10">
-        <v>271.70000000000005</v>
+        <v>127.60000000000001</v>
       </c>
       <c r="E10">
-        <v>0.98517999999999994</v>
+        <v>0.99304000000000003</v>
       </c>
       <c r="H10" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="I10" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J10">
         <v>0.29667399283427875</v>
       </c>
       <c r="K10" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L10" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P10" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="Q10" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="R10" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U10" t="s">
         <v>130</v>
       </c>
       <c r="V10" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="W10" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X10" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.45">
@@ -2112,49 +2034,49 @@
         <v>141</v>
       </c>
       <c r="C11">
-        <v>22.522200000000002</v>
+        <v>2.9493359999999997</v>
       </c>
       <c r="D11">
-        <v>118.80000000000001</v>
+        <v>266.20000000000005</v>
       </c>
       <c r="E11">
-        <v>0.99351999999999996</v>
+        <v>0.98548000000000002</v>
       </c>
       <c r="H11" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="I11" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J11">
         <v>0.21267178371296797</v>
       </c>
       <c r="K11" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L11" t="s">
+        <v>178</v>
+      </c>
+      <c r="P11" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q11" t="s">
         <v>204</v>
       </c>
-      <c r="P11" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>230</v>
-      </c>
       <c r="R11" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U11" t="s">
         <v>130</v>
       </c>
       <c r="V11" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="W11" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X11" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.45">
@@ -2162,49 +2084,49 @@
         <v>142</v>
       </c>
       <c r="C12">
-        <v>62.293548999999999</v>
+        <v>2.2790319999999999</v>
       </c>
       <c r="D12">
-        <v>111.10000000000001</v>
+        <v>203.50000000000003</v>
       </c>
       <c r="E12">
-        <v>0.99394000000000005</v>
+        <v>0.9889</v>
       </c>
       <c r="H12" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="I12" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J12">
         <v>0.11770917700286149</v>
       </c>
       <c r="K12" t="s">
+        <v>179</v>
+      </c>
+      <c r="L12" t="s">
+        <v>178</v>
+      </c>
+      <c r="P12" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q12" t="s">
         <v>205</v>
       </c>
-      <c r="L12" t="s">
-        <v>204</v>
-      </c>
-      <c r="P12" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>231</v>
-      </c>
       <c r="R12" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U12" t="s">
         <v>130</v>
       </c>
       <c r="V12" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="W12" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X12" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.45">
@@ -2212,49 +2134,49 @@
         <v>143</v>
       </c>
       <c r="C13">
-        <v>0.98311199999999999</v>
+        <v>4.7368119999999996</v>
       </c>
       <c r="D13">
-        <v>247.50000000000003</v>
+        <v>188.10000000000002</v>
       </c>
       <c r="E13">
-        <v>0.98650000000000004</v>
+        <v>0.98973999999999995</v>
       </c>
       <c r="H13" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="I13" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J13">
         <v>0.20101741572586737</v>
       </c>
       <c r="K13" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L13" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="Q13" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="R13" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U13" t="s">
         <v>130</v>
       </c>
       <c r="V13" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="W13" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X13" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.45">
@@ -2262,49 +2184,49 @@
         <v>144</v>
       </c>
       <c r="C14">
-        <v>38.43074</v>
+        <v>32.710813999999999</v>
       </c>
       <c r="D14">
-        <v>141.9</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="E14">
-        <v>0.99226000000000003</v>
+        <v>0.99838000000000005</v>
       </c>
       <c r="H14" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="I14" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J14">
         <v>0.15192763072402418</v>
       </c>
       <c r="K14" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="Q14" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="R14" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U14" t="s">
         <v>130</v>
       </c>
       <c r="V14" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="W14" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X14" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.45">
@@ -2312,49 +2234,49 @@
         <v>145</v>
       </c>
       <c r="C15">
-        <v>37.760435999999999</v>
+        <v>7.6414610000000005</v>
       </c>
       <c r="D15">
-        <v>134.20000000000002</v>
+        <v>267.3</v>
       </c>
       <c r="E15">
-        <v>0.99268000000000001</v>
+        <v>0.98541999999999996</v>
       </c>
       <c r="H15" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I15" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J15">
         <v>0.29667399283427875</v>
       </c>
       <c r="K15" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="Q15" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="R15" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U15" t="s">
         <v>130</v>
       </c>
       <c r="V15" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="W15" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X15" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.45">
@@ -2362,49 +2284,49 @@
         <v>146</v>
       </c>
       <c r="C16">
-        <v>2.9493359999999997</v>
+        <v>0.98311199999999999</v>
       </c>
       <c r="D16">
-        <v>258.5</v>
+        <v>247.50000000000003</v>
       </c>
       <c r="E16">
-        <v>0.9859</v>
+        <v>0.98650000000000004</v>
       </c>
       <c r="H16" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J16">
         <v>0.21267178371296797</v>
       </c>
       <c r="K16" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L16" t="s">
+        <v>178</v>
+      </c>
+      <c r="P16" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q16" t="s">
         <v>204</v>
       </c>
-      <c r="P16" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>230</v>
-      </c>
       <c r="R16" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s">
         <v>130</v>
       </c>
       <c r="V16" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="W16" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X16" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
@@ -2412,49 +2334,49 @@
         <v>147</v>
       </c>
       <c r="C17">
-        <v>2.2790319999999999</v>
+        <v>38.43074</v>
       </c>
       <c r="D17">
-        <v>202.4</v>
+        <v>143</v>
       </c>
       <c r="E17">
-        <v>0.98895999999999995</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H17" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="I17" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J17">
         <v>0.11770917700286149</v>
       </c>
       <c r="K17" t="s">
+        <v>179</v>
+      </c>
+      <c r="L17" t="s">
+        <v>178</v>
+      </c>
+      <c r="P17" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q17" t="s">
         <v>205</v>
       </c>
-      <c r="L17" t="s">
-        <v>204</v>
-      </c>
-      <c r="P17" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>231</v>
-      </c>
       <c r="R17" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U17" t="s">
         <v>130</v>
       </c>
       <c r="V17" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="W17" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X17" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
@@ -2462,7 +2384,7 @@
         <v>148</v>
       </c>
       <c r="C18">
-        <v>4.7368119999999996</v>
+        <v>10.412049000000001</v>
       </c>
       <c r="D18">
         <v>185.9</v>
@@ -2471,40 +2393,40 @@
         <v>0.98985999999999996</v>
       </c>
       <c r="H18" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J18">
         <v>0.20101741572586737</v>
       </c>
       <c r="K18" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="Q18" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="R18" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U18" t="s">
         <v>130</v>
       </c>
       <c r="V18" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="W18" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X18" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
@@ -2521,40 +2443,40 @@
         <v>0.99346000000000001</v>
       </c>
       <c r="H19" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="I19" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J19">
         <v>0.15192763072402418</v>
       </c>
       <c r="K19" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L19" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="Q19" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="R19" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U19" t="s">
         <v>130</v>
       </c>
       <c r="V19" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="W19" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X19" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
@@ -2571,40 +2493,40 @@
         <v>0.98787999999999998</v>
       </c>
       <c r="H20" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="I20" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J20">
         <v>0.29667399283427875</v>
       </c>
       <c r="K20" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="Q20" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="R20" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U20" t="s">
         <v>130</v>
       </c>
       <c r="V20" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="W20" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X20" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.45">
@@ -2621,40 +2543,40 @@
         <v>0.99231999999999998</v>
       </c>
       <c r="H21" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="I21" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J21">
         <v>0.21267178371296797</v>
       </c>
       <c r="K21" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L21" t="s">
+        <v>178</v>
+      </c>
+      <c r="P21" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q21" t="s">
         <v>204</v>
       </c>
-      <c r="P21" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>230</v>
-      </c>
       <c r="R21" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U21" t="s">
         <v>130</v>
       </c>
       <c r="V21" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="W21" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X21" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.45">
@@ -2671,40 +2593,40 @@
         <v>0.99238000000000004</v>
       </c>
       <c r="H22" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="I22" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J22">
         <v>0.11770917700286149</v>
       </c>
       <c r="K22" t="s">
+        <v>179</v>
+      </c>
+      <c r="L22" t="s">
+        <v>178</v>
+      </c>
+      <c r="P22" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q22" t="s">
         <v>205</v>
       </c>
-      <c r="L22" t="s">
-        <v>204</v>
-      </c>
-      <c r="P22" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>231</v>
-      </c>
       <c r="R22" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U22" t="s">
         <v>130</v>
       </c>
       <c r="V22" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="W22" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X22" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
@@ -2721,40 +2643,40 @@
         <v>0.99261999999999995</v>
       </c>
       <c r="H23" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="I23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="J23">
         <v>0.20101741572586737</v>
       </c>
       <c r="K23" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="L23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="Q23" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="R23" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="U23" t="s">
         <v>130</v>
       </c>
       <c r="V23" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="W23" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X23" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
@@ -2774,13 +2696,13 @@
         <v>130</v>
       </c>
       <c r="V24" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="W24" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X24" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
@@ -2791,22 +2713,22 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>29.700000000000003</v>
+        <v>31.900000000000002</v>
       </c>
       <c r="E25">
-        <v>0.99838000000000005</v>
+        <v>0.99826000000000004</v>
       </c>
       <c r="U25" t="s">
         <v>130</v>
       </c>
       <c r="V25" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="W25" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X25" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
@@ -2817,22 +2739,22 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>73.7</v>
+        <v>80.300000000000011</v>
       </c>
       <c r="E26">
-        <v>0.99597999999999998</v>
+        <v>0.99561999999999995</v>
       </c>
       <c r="U26" t="s">
         <v>130</v>
       </c>
       <c r="V26" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="W26" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X26" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
@@ -2843,22 +2765,22 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>24.200000000000003</v>
+        <v>18.700000000000003</v>
       </c>
       <c r="E27">
-        <v>0.99868000000000001</v>
+        <v>0.99897999999999998</v>
       </c>
       <c r="U27" t="s">
         <v>130</v>
       </c>
       <c r="V27" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="W27" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X27" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
@@ -2878,13 +2800,13 @@
         <v>130</v>
       </c>
       <c r="V28" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="W28" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X28" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
@@ -2895,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>91.300000000000011</v>
+        <v>82.5</v>
       </c>
       <c r="E29">
-        <v>0.99502000000000002</v>
+        <v>0.99550000000000005</v>
       </c>
       <c r="U29" t="s">
         <v>130</v>
       </c>
       <c r="V29" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="W29" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X29" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
@@ -2921,22 +2843,22 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>166.10000000000002</v>
+        <v>161.70000000000002</v>
       </c>
       <c r="E30">
-        <v>0.99094000000000004</v>
+        <v>0.99117999999999995</v>
       </c>
       <c r="U30" t="s">
         <v>130</v>
       </c>
       <c r="V30" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="W30" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X30" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
@@ -2956,13 +2878,13 @@
         <v>130</v>
       </c>
       <c r="V31" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="W31" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X31" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
@@ -2982,13 +2904,13 @@
         <v>130</v>
       </c>
       <c r="V32" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="W32" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X32" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.45">
@@ -3008,13 +2930,13 @@
         <v>130</v>
       </c>
       <c r="V33" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="W33" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X33" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.45">
@@ -3034,13 +2956,13 @@
         <v>130</v>
       </c>
       <c r="V34" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="W34" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X34" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.45">
@@ -3051,22 +2973,22 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>104.50000000000001</v>
+        <v>105.60000000000001</v>
       </c>
       <c r="E35">
-        <v>0.99429999999999996</v>
+        <v>0.99424000000000001</v>
       </c>
       <c r="U35" t="s">
         <v>130</v>
       </c>
       <c r="V35" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="W35" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X35" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.45">
@@ -3086,13 +3008,13 @@
         <v>130</v>
       </c>
       <c r="V36" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="W36" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X36" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.45">
@@ -3112,13 +3034,13 @@
         <v>130</v>
       </c>
       <c r="V37" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="W37" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X37" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.45">
@@ -3129,22 +3051,22 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>49.500000000000007</v>
+        <v>47.300000000000004</v>
       </c>
       <c r="E38">
-        <v>0.99729999999999996</v>
+        <v>0.99741999999999997</v>
       </c>
       <c r="U38" t="s">
         <v>130</v>
       </c>
       <c r="V38" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="W38" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X38" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.45">
@@ -3152,25 +3074,25 @@
         <v>169</v>
       </c>
       <c r="C39">
+        <v>0.98311199999999999</v>
+      </c>
+      <c r="D39">
         <v>0</v>
       </c>
-      <c r="D39">
-        <v>81.400000000000006</v>
-      </c>
       <c r="E39">
-        <v>0.99556</v>
+        <v>1</v>
       </c>
       <c r="U39" t="s">
         <v>130</v>
       </c>
       <c r="V39" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="W39" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X39" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.45">
@@ -3178,25 +3100,25 @@
         <v>170</v>
       </c>
       <c r="C40">
+        <v>8.1330170000000006</v>
+      </c>
+      <c r="D40">
         <v>0</v>
       </c>
-      <c r="D40">
-        <v>96.800000000000011</v>
-      </c>
       <c r="E40">
-        <v>0.99472000000000005</v>
+        <v>1</v>
       </c>
       <c r="U40" t="s">
         <v>130</v>
       </c>
       <c r="V40" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="W40" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X40" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.45">
@@ -3204,25 +3126,25 @@
         <v>171</v>
       </c>
       <c r="C41">
+        <v>0.49155599999999999</v>
+      </c>
+      <c r="D41">
         <v>0</v>
       </c>
-      <c r="D41">
-        <v>128.70000000000002</v>
-      </c>
       <c r="E41">
-        <v>0.99297999999999997</v>
+        <v>1</v>
       </c>
       <c r="U41" t="s">
         <v>130</v>
       </c>
       <c r="V41" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="W41" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X41" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.45">
@@ -3230,869 +3152,557 @@
         <v>172</v>
       </c>
       <c r="C42">
+        <v>3.5749529999999998</v>
+      </c>
+      <c r="D42">
         <v>0</v>
       </c>
-      <c r="D42">
-        <v>127.60000000000001</v>
-      </c>
       <c r="E42">
-        <v>0.99304000000000003</v>
+        <v>1</v>
       </c>
       <c r="U42" t="s">
         <v>130</v>
       </c>
       <c r="V42" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="W42" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X42" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>173</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>73.7</v>
-      </c>
-      <c r="E43">
-        <v>0.99597999999999998</v>
-      </c>
       <c r="U43" t="s">
         <v>130</v>
       </c>
       <c r="V43" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="W43" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X43" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>174</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>105.60000000000001</v>
-      </c>
-      <c r="E44">
-        <v>0.99424000000000001</v>
-      </c>
       <c r="U44" t="s">
         <v>130</v>
       </c>
       <c r="V44" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="W44" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X44" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>175</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>38.5</v>
-      </c>
-      <c r="E45">
-        <v>0.99790000000000001</v>
-      </c>
       <c r="U45" t="s">
         <v>130</v>
       </c>
       <c r="V45" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="W45" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X45" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>176</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>138.60000000000002</v>
-      </c>
-      <c r="E46">
-        <v>0.99243999999999999</v>
-      </c>
       <c r="U46" t="s">
         <v>130</v>
       </c>
       <c r="V46" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="W46" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X46" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>177</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>147.4</v>
-      </c>
-      <c r="E47">
-        <v>0.99195999999999995</v>
-      </c>
       <c r="U47" t="s">
         <v>130</v>
       </c>
       <c r="V47" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="W47" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X47" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>178</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>73.7</v>
-      </c>
-      <c r="E48">
-        <v>0.99597999999999998</v>
-      </c>
       <c r="U48" t="s">
         <v>130</v>
       </c>
       <c r="V48" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="W48" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X48" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>37.400000000000006</v>
-      </c>
-      <c r="E49">
-        <v>0.99795999999999996</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U49" t="s">
         <v>130</v>
       </c>
       <c r="V49" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="W49" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X49" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>180</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>103.4</v>
-      </c>
-      <c r="E50">
-        <v>0.99436000000000002</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U50" t="s">
         <v>130</v>
       </c>
       <c r="V50" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="W50" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X50" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>181</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>129.80000000000001</v>
-      </c>
-      <c r="E51">
-        <v>0.99292000000000002</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U51" t="s">
         <v>130</v>
       </c>
       <c r="V51" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="W51" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X51" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>124.30000000000001</v>
-      </c>
-      <c r="E52">
-        <v>0.99321999999999999</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U52" t="s">
         <v>130</v>
       </c>
       <c r="V52" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="W52" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X52" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53">
-        <v>0.98311199999999999</v>
-      </c>
-      <c r="D53">
-        <v>103.4</v>
-      </c>
-      <c r="E53">
-        <v>0.99436000000000002</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U53" t="s">
         <v>130</v>
       </c>
       <c r="V53" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="W53" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X53" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>184</v>
-      </c>
-      <c r="C54">
-        <v>8.1330170000000006</v>
-      </c>
-      <c r="D54">
-        <v>78.100000000000009</v>
-      </c>
-      <c r="E54">
-        <v>0.99573999999999996</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U54" t="s">
         <v>130</v>
       </c>
       <c r="V54" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="W54" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X54" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>185</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>108.9</v>
-      </c>
-      <c r="E55">
-        <v>0.99406000000000005</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U55" t="s">
         <v>130</v>
       </c>
       <c r="V55" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="W55" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X55" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>186</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>144.10000000000002</v>
-      </c>
-      <c r="E56">
-        <v>0.99214000000000002</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U56" t="s">
         <v>130</v>
       </c>
       <c r="V56" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="W56" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X56" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>187</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>159.5</v>
-      </c>
-      <c r="E57">
-        <v>0.99129999999999996</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U57" t="s">
         <v>130</v>
       </c>
       <c r="V57" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="W57" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X57" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>188</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>135.30000000000001</v>
-      </c>
-      <c r="E58">
-        <v>0.99261999999999995</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U58" t="s">
         <v>130</v>
       </c>
       <c r="V58" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="W58" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X58" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>189</v>
-      </c>
-      <c r="C59">
-        <v>0.49155599999999999</v>
-      </c>
-      <c r="D59">
-        <v>218.9</v>
-      </c>
-      <c r="E59">
-        <v>0.98806000000000005</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U59" t="s">
         <v>130</v>
       </c>
       <c r="V59" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="W59" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X59" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>190</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>52.800000000000004</v>
-      </c>
-      <c r="E60">
-        <v>0.99712000000000001</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U60" t="s">
         <v>130</v>
       </c>
       <c r="V60" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="W60" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X60" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>191</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>57.2</v>
-      </c>
-      <c r="E61">
-        <v>0.99687999999999999</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U61" t="s">
         <v>130</v>
       </c>
       <c r="V61" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="W61" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X61" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>192</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>74.800000000000011</v>
-      </c>
-      <c r="E62">
-        <v>0.99592000000000003</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U62" t="s">
         <v>130</v>
       </c>
       <c r="V62" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="W62" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X62" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>193</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>133.10000000000002</v>
-      </c>
-      <c r="E63">
-        <v>0.99273999999999996</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U63" t="s">
         <v>130</v>
       </c>
       <c r="V63" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="W63" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X63" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>194</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>174.9</v>
-      </c>
-      <c r="E64">
-        <v>0.99046000000000001</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U64" t="s">
         <v>130</v>
       </c>
       <c r="V64" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="W64" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X64" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
-        <v>26.400000000000002</v>
-      </c>
-      <c r="E65">
-        <v>0.99856</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U65" t="s">
         <v>130</v>
       </c>
       <c r="V65" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="W65" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X65" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>84.7</v>
-      </c>
-      <c r="E66">
-        <v>0.99538000000000004</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U66" t="s">
         <v>130</v>
       </c>
       <c r="V66" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="W66" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X66" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B67" t="s">
-        <v>197</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>193.60000000000002</v>
-      </c>
-      <c r="E67">
-        <v>0.98943999999999999</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U67" t="s">
         <v>130</v>
       </c>
       <c r="V67" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="W67" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X67" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.45">
-      <c r="B68" t="s">
-        <v>198</v>
-      </c>
-      <c r="C68">
-        <v>3.5749529999999998</v>
-      </c>
-      <c r="D68">
-        <v>41.800000000000004</v>
-      </c>
-      <c r="E68">
-        <v>0.99772000000000005</v>
-      </c>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U68" t="s">
         <v>130</v>
       </c>
       <c r="V68" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="W68" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X68" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U69" t="s">
         <v>130</v>
       </c>
       <c r="V69" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="W69" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X69" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U70" t="s">
         <v>130</v>
       </c>
       <c r="V70" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="W70" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X70" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U71" t="s">
         <v>130</v>
       </c>
       <c r="V71" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="W71" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X71" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U72" t="s">
         <v>130</v>
       </c>
       <c r="V72" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="W72" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X72" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U73" t="s">
         <v>130</v>
       </c>
       <c r="V73" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="W73" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X73" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U74" t="s">
         <v>130</v>
       </c>
       <c r="V74" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="W74" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X74" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U75" t="s">
         <v>130</v>
       </c>
       <c r="V75" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="W75" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="X75" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U76" t="s">
         <v>130</v>
       </c>
       <c r="V76" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="W76" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="X76" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U77" t="s">
         <v>130</v>
       </c>
       <c r="V77" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="W77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="X77" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U78" t="s">
         <v>130</v>
       </c>
       <c r="V78" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="W78" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="X78" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U79" t="s">
         <v>130</v>
       </c>
       <c r="V79" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="W79" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="X79" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U80" t="s">
         <v>130</v>
       </c>
       <c r="V80" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="W80" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="X80" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="21:24" x14ac:dyDescent="0.45">
@@ -4100,13 +3710,13 @@
         <v>130</v>
       </c>
       <c r="V81" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="W81" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X81" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="21:24" x14ac:dyDescent="0.45">
@@ -4114,13 +3724,13 @@
         <v>130</v>
       </c>
       <c r="V82" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="W82" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X82" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="21:24" x14ac:dyDescent="0.45">
@@ -4128,13 +3738,13 @@
         <v>130</v>
       </c>
       <c r="V83" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="W83" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X83" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="21:24" x14ac:dyDescent="0.45">
@@ -4142,13 +3752,13 @@
         <v>130</v>
       </c>
       <c r="V84" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="W84" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X84" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="21:24" x14ac:dyDescent="0.45">
@@ -4156,13 +3766,13 @@
         <v>130</v>
       </c>
       <c r="V85" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="W85" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="X85" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="21:24" x14ac:dyDescent="0.45">
@@ -4170,13 +3780,13 @@
         <v>130</v>
       </c>
       <c r="V86" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="W86" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X86" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87" spans="21:24" x14ac:dyDescent="0.45">
@@ -4184,13 +3794,13 @@
         <v>130</v>
       </c>
       <c r="V87" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="W87" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="X87" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88" spans="21:24" x14ac:dyDescent="0.45">
@@ -4198,13 +3808,13 @@
         <v>130</v>
       </c>
       <c r="V88" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="W88" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X88" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="21:24" x14ac:dyDescent="0.45">
@@ -4212,13 +3822,13 @@
         <v>130</v>
       </c>
       <c r="V89" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="W89" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="X89" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="90" spans="21:24" x14ac:dyDescent="0.45">
@@ -4226,13 +3836,13 @@
         <v>130</v>
       </c>
       <c r="V90" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="W90" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X90" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" spans="21:24" x14ac:dyDescent="0.45">
@@ -4240,13 +3850,13 @@
         <v>130</v>
       </c>
       <c r="V91" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="W91" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="X91" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="21:24" x14ac:dyDescent="0.45">
@@ -4254,13 +3864,13 @@
         <v>130</v>
       </c>
       <c r="V92" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="W92" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X92" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="21:24" x14ac:dyDescent="0.45">
@@ -4268,13 +3878,13 @@
         <v>130</v>
       </c>
       <c r="V93" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="W93" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="X93" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4283,7 +3893,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E56863-42AA-48A3-80B6-26F1DE6220F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6EBD1C-5E7E-47D2-A19B-46A5799BF805}">
   <dimension ref="B9:L88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
